--- a/pre-week-2/Homework 2.xlsx
+++ b/pre-week-2/Homework 2.xlsx
@@ -8,14 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kendratyler\Documents\dataanalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CC2E253-BAD0-4F3F-BFB0-27662F2188A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13353D13-C821-4545-A819-24A3753C6BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="400" windowWidth="9380" windowHeight="11220" xr2:uid="{EB6DDC52-CA86-4AA5-B839-D0E7C2CDFF66}"/>
+    <workbookView xWindow="7700" yWindow="160" windowWidth="11000" windowHeight="11220" xr2:uid="{EB6DDC52-CA86-4AA5-B839-D0E7C2CDFF66}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Store_Region_Sumary" sheetId="5" r:id="rId1"/>
+    <sheet name="Store_Region_Summary" sheetId="6" r:id="rId2"/>
+    <sheet name="Store_Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Store_Category_Summary" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="23" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,10 +41,113 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Monthly Sales</t>
+  </si>
+  <si>
+    <t>Store A</t>
+  </si>
+  <si>
+    <t>Store B</t>
+  </si>
+  <si>
+    <t>Store C</t>
+  </si>
+  <si>
+    <t>Store D</t>
+  </si>
+  <si>
+    <t>Store E</t>
+  </si>
+  <si>
+    <t>Store F</t>
+  </si>
+  <si>
+    <t>Store G</t>
+  </si>
+  <si>
+    <t>Store H</t>
+  </si>
+  <si>
+    <t>Store I</t>
+  </si>
+  <si>
+    <t>Store J</t>
+  </si>
+  <si>
+    <t>Store K</t>
+  </si>
+  <si>
+    <t>Store L</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>Electrioncs</t>
+  </si>
+  <si>
+    <t>Home Goods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Electrioncs with 72 </t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Monthly Sales</t>
+  </si>
+  <si>
+    <t>A) Which Category performs best ?  The west Region , but none of them make it to 30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C) The pie chart isnt that hard to understand. You can roll your cursor over to see the precentage. It comes in 4 different colors. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B) I selected that pie chart because it was the best looking one for me. Its east to understand. </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -66,8 +175,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -83,6 +215,2473 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Homework 2.xlsx]Store_Region_Sumary!PivotTable6</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Store_Region_Sumary!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:sysClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Store_Region_Sumary!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Store_Region_Sumary!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>167</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3F17-4A2C-A194-7DE01484D5B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Homework 2.xlsx]Store_Region_Summary!PivotTable7</c:name>
+    <c:fmtId val="26"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Store_Region_Summary!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Store_Region_Summary!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Apparel</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electrioncs</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Home Goods</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Store_Region_Summary!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-19C9-43C8-BC00-B106D86F4753}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="344">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>143878</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>147722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>142040</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>175461</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F18689A-F9CE-BC42-FA94-EB39ADEDE096}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>937381</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>90713</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>40317</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83970C2A-8BFE-7D5C-16C2-F4FE9D0DA99E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="kendra tyler" refreshedDate="46111.447775000001" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{0173C55D-5876-42BE-92CB-1C3C38EFB383}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:D13" sheet="Store_Data"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Store" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="West"/>
+        <s v="East"/>
+        <s v="North"/>
+        <s v="South"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Electrioncs"/>
+        <s v="Apparel"/>
+        <s v="Home Goods"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Monthly Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="43" maxValue="72"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <s v="Store H"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="72"/>
+  </r>
+  <r>
+    <s v="Store E"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="52"/>
+  </r>
+  <r>
+    <s v="Store A"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="51"/>
+  </r>
+  <r>
+    <s v="Store L"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="50"/>
+  </r>
+  <r>
+    <s v="Store C"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="49"/>
+  </r>
+  <r>
+    <s v="Store J"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="48"/>
+  </r>
+  <r>
+    <s v="Store F"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="47"/>
+  </r>
+  <r>
+    <s v="Store D"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <s v="Store K"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="46"/>
+  </r>
+  <r>
+    <s v="Store G"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="45"/>
+  </r>
+  <r>
+    <s v="Store B"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="44"/>
+  </r>
+  <r>
+    <s v="Store I"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="43"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B75D929-23BC-4792-8DBC-EAF33A271550}" name="PivotTable6" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly Sales" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FA1BA40-0EBF-47CD-8B56-D44BF2128AB1}" name="PivotTable7" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Monthly Sales" fld="3" baseField="2" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="26" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,10 +3000,556 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F3159C-A7A9-4CDC-9FC5-4F4D01BDF06E}">
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="8">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="8">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="8">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="8">
+        <v>593</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD84BB6-C41C-4D49-833A-0AF60E07ABA6}">
+  <dimension ref="A3:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="8">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="8">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="8">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="8">
+        <v>593</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70663D6C-C0BA-4EBB-8FB8-02F71BB0B421}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D13">
+    <sortCondition descending="1" ref="D14:D13"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E7C835-BC48-4D4A-BC6D-86E14B4D8C88}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="69.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006BAB7F1D75092C43A80735B994755528" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9170d54eb2f2fe8c698f119f42bbfd49">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b275f972-a0ec-44ed-acfc-93b347ca42d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="41f6f991b53f8449fa16e35e2d68b8e7" ns3:_="">
+    <xsd:import namespace="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b275f972-a0ec-44ed-acfc-93b347ca42d1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D375882F-7D93-43E1-B111-44E27CE8C921}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{257CAB96-A3D4-4876-A72E-7B3502D52178}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{946A11EC-2019-48C1-B706-B9182A3B890D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/pre-week-2/Homework 2.xlsx
+++ b/pre-week-2/Homework 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kendratyler\Documents\dataanalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13353D13-C821-4545-A819-24A3753C6BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9DBE7CD-4D55-44A6-80C7-FFFF92D5B8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7700" yWindow="160" windowWidth="11000" windowHeight="11220" xr2:uid="{EB6DDC52-CA86-4AA5-B839-D0E7C2CDFF66}"/>
   </bookViews>
